--- a/assets/sandbox.xlsx
+++ b/assets/sandbox.xlsx
@@ -7,14 +7,14 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Справка" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Заказы" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сотрудники" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Часы" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Выгрузка" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Архив" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сводка" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Настройки" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Help" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orders" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Employees" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hours" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Archive" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Settings" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -458,7 +458,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Учебная таблица курса «Скрипты для Google Таблиц»</t>
+          <t>Course sandbox: Google Sheets Scripts</t>
         </is>
       </c>
     </row>
@@ -468,14 +468,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Перед работой: Файл → Создать копию. Все скрипты курса запускаются на копии.</t>
+          <t>Before you start: File → Make a copy. Run every course script on your copy.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Все имена, email и цифры вымышлены. Совпадения с реальными людьми случайны.</t>
+          <t>All names, emails and numbers are fictional. Any resemblance to real people is coincidental.</t>
         </is>
       </c>
     </row>
@@ -485,136 +485,136 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Лист</t>
+          <t>Sheet</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Что внутри</t>
+          <t>What's inside</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Где используется</t>
+          <t>Used in</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Заказы</t>
+          <t>Orders</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>200 заказов за 3 месяца: даты, дедлайны, статусы, исполнители, часы, оценки QC</t>
+          <t>200 orders over 3 months: dates, deadlines, statuses, assignees, hours, QC scores</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Модули 2, 3, 5, 6, 8</t>
+          <t>Modules 2, 3, 5, 6, 8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Сотрудники</t>
+          <t>Employees</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>30 составителей: команда, страна, супервайзер, вымышленный email</t>
+          <t>30 drafters: team, country, supervisor, fictional email</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Модули 5, 6, 7</t>
+          <t>Modules 5, 6, 7</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Часы</t>
+          <t>Hours</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Рабочие и залогированные часы по неделям</t>
+          <t>Worked and logged hours by week</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Модули 6, 8</t>
+          <t>Modules 6, 8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Выгрузка</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>«Грязная» выгрузка: пробелы, регистр, дубли, пустые строки, даты текстом</t>
+          <t>A messy export: extra spaces, mixed case, duplicates, empty rows, dates as text</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Модули 2, 6</t>
+          <t>Modules 2, 6</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Архив</t>
+          <t>Archive</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Пустой лист для закрытых заказов</t>
+          <t>Empty sheet for closed orders</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Модуль 5</t>
+          <t>Module 5</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Сводка</t>
+          <t>Summary</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Пустой лист для метрик и графиков</t>
+          <t>Empty sheet for metrics and charts</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Модуль 8</t>
+          <t>Module 8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Настройки</t>
+          <t>Settings</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Параметры, которые читают скрипты: имена листов, пороги, адреса</t>
+          <t>Parameters the scripts read: sheet names, thresholds, addresses</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Модули 1, 5</t>
+          <t>Modules 1, 5</t>
         </is>
       </c>
     </row>
@@ -649,62 +649,62 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>ID заказа</t>
+          <t>Order ID</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>Создан</t>
+          <t>Created</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Дедлайн</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Тип</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Статус</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>ID исполнителя</t>
+          <t>Assignee ID</t>
         </is>
       </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Исполнитель</t>
+          <t>Assignee</t>
         </is>
       </c>
       <c r="H1" s="3" t="inlineStr">
         <is>
-          <t>Супервайзер</t>
+          <t>Supervisor</t>
         </is>
       </c>
       <c r="I1" s="3" t="inlineStr">
         <is>
-          <t>Часы</t>
+          <t>Hours</t>
         </is>
       </c>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Оценка QC</t>
+          <t>QC Score</t>
         </is>
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
-          <t>Сдан</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
-          <t>Комментарий</t>
+          <t>Comment</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Глеб Г.</t>
+          <t>Gleb G.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -775,7 +775,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Тимур С.</t>
+          <t>Timur S.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -823,7 +823,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ева С.</t>
+          <t>Eva S.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="I4" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Кирилл П.</t>
+          <t>Kirill P.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I5" t="n">
@@ -919,7 +919,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ян Г.</t>
+          <t>Yan G.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="I6" t="n">
@@ -967,7 +967,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Юлия В.</t>
+          <t>Julia V.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1025,12 +1025,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Марк О.</t>
+          <t>Mark O.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Клиент просил ускорить</t>
+          <t>Client asked to rush</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1077,12 +1077,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Кирилл П.</t>
+          <t>Kirill P.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I9" t="n">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Кирилл П.</t>
+          <t>Kirill P.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I10" t="n">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1173,12 +1173,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Дарья М.</t>
+          <t>Daria M.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Захар Л.</t>
+          <t>Zakhar L.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I12" t="n">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Повторная проверка</t>
+          <t>Second review</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1263,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Юлия В.</t>
+          <t>Julia V.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I13" t="n">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1325,12 +1325,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Вера Ш.</t>
+          <t>Vera W.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Алекс Г.</t>
+          <t>Alex G.</t>
         </is>
       </c>
       <c r="I14" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Клиент просил ускорить</t>
+          <t>Client asked to rush</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1377,12 +1377,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Тина Е.</t>
+          <t>Tina E.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I15" t="n">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ольга Л.</t>
+          <t>Olga L.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Нужны доп. фото</t>
+          <t>More photos needed</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Проблема</t>
+          <t>Problem</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1477,12 +1477,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ян Г.</t>
+          <t>Yan G.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1520,12 +1520,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ник С.</t>
+          <t>Nick S.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1568,12 +1568,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ульяна Л.</t>
+          <t>Ulyana L.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Глеб М.</t>
+          <t>Gleb M.</t>
         </is>
       </c>
       <c r="I19" t="n">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Нужны доп. фото</t>
+          <t>More photos needed</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1620,12 +1620,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ева С.</t>
+          <t>Eva S.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="I20" t="n">
@@ -1639,7 +1639,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Нужны доп. фото</t>
+          <t>More photos needed</t>
         </is>
       </c>
     </row>
@@ -1662,7 +1662,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1672,12 +1672,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Захар Л.</t>
+          <t>Zakhar L.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I21" t="n">
@@ -1710,7 +1710,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1720,12 +1720,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Роман Ш.</t>
+          <t>Roman W.</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Вера Ш.</t>
+          <t>Vera W.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Алекс Г.</t>
+          <t>Alex G.</t>
         </is>
       </c>
       <c r="I23" t="n">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Нужны доп. фото</t>
+          <t>More photos needed</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Софья С.</t>
+          <t>Sofia S.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I24" t="n">
@@ -1858,7 +1858,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1868,12 +1868,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Марк О.</t>
+          <t>Mark O.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="I25" t="n">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1916,12 +1916,12 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Вера Ш.</t>
+          <t>Vera W.</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Алекс Г.</t>
+          <t>Alex G.</t>
         </is>
       </c>
       <c r="I26" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Повторная проверка</t>
+          <t>Second review</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Жанна В.</t>
+          <t>Jeanne V.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Глеб М.</t>
+          <t>Gleb M.</t>
         </is>
       </c>
       <c r="I27" t="n">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Клиент просил ускорить</t>
+          <t>Client asked to rush</t>
         </is>
       </c>
     </row>
@@ -2010,7 +2010,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Проблема</t>
+          <t>Problem</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Юлия В.</t>
+          <t>Julia V.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -2053,7 +2053,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2063,12 +2063,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Тина Е.</t>
+          <t>Tina E.</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Захар Л.</t>
+          <t>Zakhar L.</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Нина Х.</t>
+          <t>Nina H.</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Глеб М.</t>
+          <t>Gleb M.</t>
         </is>
       </c>
       <c r="I31" t="n">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2215,12 +2215,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Нина Х.</t>
+          <t>Nina H.</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Глеб М.</t>
+          <t>Gleb M.</t>
         </is>
       </c>
       <c r="I32" t="n">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Роман Ш.</t>
+          <t>Roman W.</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I33" t="n">
@@ -2301,7 +2301,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2311,12 +2311,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Юлия В.</t>
+          <t>Julia V.</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Клиент просил ускорить</t>
+          <t>Client asked to rush</t>
         </is>
       </c>
     </row>
@@ -2353,7 +2353,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Проблема</t>
+          <t>Problem</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2363,12 +2363,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Вера Ш.</t>
+          <t>Vera W.</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Алекс Г.</t>
+          <t>Alex G.</t>
         </is>
       </c>
       <c r="I35" t="n">
@@ -2377,7 +2377,7 @@
       <c r="K35" s="4" t="n"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -2400,7 +2400,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2410,12 +2410,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Юлия В.</t>
+          <t>Julia V.</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I36" t="n">
@@ -2448,7 +2448,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2458,12 +2458,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Ник С.</t>
+          <t>Nick S.</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I37" t="n">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Жанна В.</t>
+          <t>Jeanne V.</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Глеб М.</t>
+          <t>Gleb M.</t>
         </is>
       </c>
       <c r="I38" t="n">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Нужны доп. фото</t>
+          <t>More photos needed</t>
         </is>
       </c>
     </row>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2558,12 +2558,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Вера Ш.</t>
+          <t>Vera W.</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Алекс Г.</t>
+          <t>Alex G.</t>
         </is>
       </c>
       <c r="I39" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Борис Х.</t>
+          <t>Boris H.</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I40" t="n">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2654,12 +2654,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Ник С.</t>
+          <t>Nick S.</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I41" t="n">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2702,12 +2702,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ирина А.</t>
+          <t>Irina A.</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Алекс Г.</t>
+          <t>Alex G.</t>
         </is>
       </c>
       <c r="I42" t="n">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Фёдор С.</t>
+          <t>Fedor S.</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -2788,7 +2788,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Ник С.</t>
+          <t>Nick S.</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I44" t="n">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -2840,7 +2840,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Борис Х.</t>
+          <t>Boris H.</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I45" t="n">
@@ -2888,7 +2888,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2898,12 +2898,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Анна П.</t>
+          <t>Anna P.</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Глеб М.</t>
+          <t>Gleb M.</t>
         </is>
       </c>
       <c r="I46" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2946,12 +2946,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Майя Д.</t>
+          <t>Maya D.</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I47" t="n">
@@ -2984,7 +2984,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2994,12 +2994,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Егор Н.</t>
+          <t>Egor N.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="I48" t="n">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Клиент просил ускорить</t>
+          <t>Client asked to rush</t>
         </is>
       </c>
     </row>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3046,12 +3046,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Захар Л.</t>
+          <t>Zakhar L.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3088,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Юлия В.</t>
+          <t>Julia V.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I50" t="n">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Ян Г.</t>
+          <t>Yan G.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="I51" t="n">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3194,12 +3194,12 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Лиана Г.</t>
+          <t>Liana G.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I52" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Повторная проверка</t>
+          <t>Second review</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Юлия В.</t>
+          <t>Julia V.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I53" t="n">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Жанна В.</t>
+          <t>Jeanne V.</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Глеб М.</t>
+          <t>Gleb M.</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -3336,7 +3336,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -3346,12 +3346,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Роман Ш.</t>
+          <t>Roman W.</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I55" t="n">
@@ -3365,7 +3365,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Нужны доп. фото</t>
+          <t>More photos needed</t>
         </is>
       </c>
     </row>
@@ -3388,7 +3388,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Фёдор С.</t>
+          <t>Fedor S.</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I56" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -3446,12 +3446,12 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Кирилл П.</t>
+          <t>Kirill P.</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I57" t="n">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Повторная проверка</t>
+          <t>Second review</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -3498,12 +3498,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Анна П.</t>
+          <t>Anna P.</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Глеб М.</t>
+          <t>Gleb M.</t>
         </is>
       </c>
       <c r="I58" t="n">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Тина Е.</t>
+          <t>Tina E.</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I59" t="n">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ева С.</t>
+          <t>Eva S.</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="I60" t="n">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Нужны доп. фото</t>
+          <t>More photos needed</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Софья С.</t>
+          <t>Sofia S.</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I61" t="n">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -3694,12 +3694,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Кирилл П.</t>
+          <t>Kirill P.</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I62" t="n">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Марк О.</t>
+          <t>Mark O.</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="I63" t="n">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -3784,7 +3784,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Кирилл П.</t>
+          <t>Kirill P.</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I64" t="n">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -3842,12 +3842,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Фёдор С.</t>
+          <t>Fedor S.</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I65" t="n">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ник С.</t>
+          <t>Nick S.</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I66" t="n">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Клиент просил ускорить</t>
+          <t>Client asked to rush</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ирина А.</t>
+          <t>Irina A.</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Алекс Г.</t>
+          <t>Alex G.</t>
         </is>
       </c>
       <c r="I67" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -3984,7 +3984,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3994,12 +3994,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Борис Х.</t>
+          <t>Boris H.</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I68" t="n">
@@ -4032,7 +4032,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -4042,12 +4042,12 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Лиана Г.</t>
+          <t>Liana G.</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I69" t="n">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Повторная проверка</t>
+          <t>Second review</t>
         </is>
       </c>
     </row>
@@ -4084,7 +4084,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -4094,12 +4094,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Борис Х.</t>
+          <t>Boris H.</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -4142,12 +4142,12 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Софья С.</t>
+          <t>Sofia S.</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I71" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Юлия В.</t>
+          <t>Julia V.</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I72" t="n">
@@ -4232,7 +4232,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Софья С.</t>
+          <t>Sofia S.</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I73" t="n">
@@ -4261,7 +4261,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Лев П.</t>
+          <t>Leo P.</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Глеб М.</t>
+          <t>Gleb M.</t>
         </is>
       </c>
       <c r="I74" t="n">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ирина А.</t>
+          <t>Irina A.</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Алекс Г.</t>
+          <t>Alex G.</t>
         </is>
       </c>
       <c r="I75" t="n">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Глеб Г.</t>
+          <t>Gleb G.</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I76" t="n">
@@ -4428,7 +4428,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Борис Х.</t>
+          <t>Boris H.</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I77" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4486,12 +4486,12 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ева С.</t>
+          <t>Eva S.</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="I78" t="n">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Нужны доп. фото</t>
+          <t>More photos needed</t>
         </is>
       </c>
     </row>
@@ -4528,7 +4528,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Фёдор С.</t>
+          <t>Fedor S.</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I79" t="n">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -4586,12 +4586,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Борис Х.</t>
+          <t>Boris H.</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I80" t="n">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Жанна В.</t>
+          <t>Jeanne V.</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Глеб М.</t>
+          <t>Gleb M.</t>
         </is>
       </c>
       <c r="I81" t="n">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ольга Л.</t>
+          <t>Olga L.</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I82" t="n">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -4730,12 +4730,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ян Г.</t>
+          <t>Yan G.</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="I83" t="n">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Кирилл П.</t>
+          <t>Kirill P.</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I84" t="n">
@@ -4797,7 +4797,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Повторная проверка</t>
+          <t>Second review</t>
         </is>
       </c>
     </row>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4830,12 +4830,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Алекс Л.</t>
+          <t>Alex L.</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Алекс Г.</t>
+          <t>Alex G.</t>
         </is>
       </c>
       <c r="I85" t="n">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Софья С.</t>
+          <t>Sofia S.</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I86" t="n">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Нужны доп. фото</t>
+          <t>More photos needed</t>
         </is>
       </c>
     </row>
@@ -4920,7 +4920,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4930,12 +4930,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Борис Х.</t>
+          <t>Boris H.</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I87" t="n">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Юлия В.</t>
+          <t>Julia V.</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I88" t="n">
@@ -5020,7 +5020,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -5030,12 +5030,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Дарья М.</t>
+          <t>Daria M.</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I89" t="n">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5078,12 +5078,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Борис Х.</t>
+          <t>Boris H.</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I90" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Глеб Г.</t>
+          <t>Gleb G.</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I91" t="n">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Нужны доп. фото</t>
+          <t>More photos needed</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Кирилл П.</t>
+          <t>Kirill P.</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I92" t="n">
@@ -5216,7 +5216,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -5226,12 +5226,12 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Марк О.</t>
+          <t>Mark O.</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="I93" t="n">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Повторная проверка</t>
+          <t>Second review</t>
         </is>
       </c>
     </row>
@@ -5268,7 +5268,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Вера Ш.</t>
+          <t>Vera W.</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Алекс Г.</t>
+          <t>Alex G.</t>
         </is>
       </c>
       <c r="I94" t="n">
@@ -5297,7 +5297,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Повторная проверка</t>
+          <t>Second review</t>
         </is>
       </c>
     </row>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Нина Х.</t>
+          <t>Nina H.</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Глеб М.</t>
+          <t>Gleb M.</t>
         </is>
       </c>
       <c r="I95" t="n">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -5378,12 +5378,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Егор Н.</t>
+          <t>Egor N.</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="I96" t="n">
@@ -5416,7 +5416,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Глеб Г.</t>
+          <t>Gleb G.</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I97" t="n">
@@ -5445,7 +5445,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Нужны доп. фото</t>
+          <t>More photos needed</t>
         </is>
       </c>
     </row>
@@ -5468,7 +5468,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ян Г.</t>
+          <t>Yan G.</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="I98" t="n">
@@ -5497,7 +5497,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Повторная проверка</t>
+          <t>Second review</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -5530,12 +5530,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Тина Е.</t>
+          <t>Tina E.</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I99" t="n">
@@ -5568,7 +5568,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Дарья М.</t>
+          <t>Daria M.</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I100" t="n">
@@ -5597,7 +5597,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -5630,12 +5630,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Алекс Л.</t>
+          <t>Alex L.</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Алекс Г.</t>
+          <t>Alex G.</t>
         </is>
       </c>
       <c r="I101" t="n">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -5678,12 +5678,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Лиана Г.</t>
+          <t>Liana G.</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I102" t="n">
@@ -5716,7 +5716,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Кирилл П.</t>
+          <t>Kirill P.</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I103" t="n">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ирина А.</t>
+          <t>Irina A.</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Алекс Г.</t>
+          <t>Alex G.</t>
         </is>
       </c>
       <c r="I104" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -5816,7 +5816,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Глеб Г.</t>
+          <t>Gleb G.</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I105" t="n">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -5874,12 +5874,12 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Алекс Л.</t>
+          <t>Alex L.</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Алекс Г.</t>
+          <t>Alex G.</t>
         </is>
       </c>
       <c r="I106" t="n">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Тина Е.</t>
+          <t>Tina E.</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I107" t="n">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Жанна В.</t>
+          <t>Jeanne V.</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Глеб М.</t>
+          <t>Gleb M.</t>
         </is>
       </c>
       <c r="I108" t="n">
@@ -6008,7 +6008,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Проблема</t>
+          <t>Problem</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Кирилл П.</t>
+          <t>Kirill P.</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I109" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Сергей Р.</t>
+          <t>Sergey R.</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Алекс Г.</t>
+          <t>Alex G.</t>
         </is>
       </c>
       <c r="I110" t="n">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Нужны доп. фото</t>
+          <t>More photos needed</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Проблема</t>
+          <t>Problem</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Нина Х.</t>
+          <t>Nina H.</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Глеб М.</t>
+          <t>Gleb M.</t>
         </is>
       </c>
       <c r="I111" t="n">
@@ -6127,7 +6127,7 @@
       <c r="K111" s="4" t="n"/>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -6150,7 +6150,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -6160,12 +6160,12 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Тина Е.</t>
+          <t>Tina E.</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I112" t="n">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -6208,12 +6208,12 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ирина А.</t>
+          <t>Irina A.</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Алекс Г.</t>
+          <t>Alex G.</t>
         </is>
       </c>
       <c r="I113" t="n">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Нужны доп. фото</t>
+          <t>More photos needed</t>
         </is>
       </c>
     </row>
@@ -6250,7 +6250,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Нина Х.</t>
+          <t>Nina H.</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Глеб М.</t>
+          <t>Gleb M.</t>
         </is>
       </c>
       <c r="I114" t="n">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -6308,12 +6308,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Борис Х.</t>
+          <t>Boris H.</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I115" t="n">
@@ -6346,7 +6346,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Юлия В.</t>
+          <t>Julia V.</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I116" t="n">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Клиент просил ускорить</t>
+          <t>Client asked to rush</t>
         </is>
       </c>
     </row>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -6408,12 +6408,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ульяна Л.</t>
+          <t>Ulyana L.</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Глеб М.</t>
+          <t>Gleb M.</t>
         </is>
       </c>
       <c r="I117" t="n">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Лиана Г.</t>
+          <t>Liana G.</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I118" t="n">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Клиент просил ускорить</t>
+          <t>Client asked to rush</t>
         </is>
       </c>
     </row>
@@ -6502,7 +6502,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -6512,12 +6512,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ник С.</t>
+          <t>Nick S.</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I119" t="n">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -6564,12 +6564,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Дарья М.</t>
+          <t>Daria M.</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I120" t="n">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -6616,12 +6616,12 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Захар Л.</t>
+          <t>Zakhar L.</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I121" t="n">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Лев П.</t>
+          <t>Leo P.</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Глеб М.</t>
+          <t>Gleb M.</t>
         </is>
       </c>
       <c r="I122" t="n">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>Нужны доп. фото</t>
+          <t>More photos needed</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6706,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Вера Ш.</t>
+          <t>Vera W.</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Алекс Г.</t>
+          <t>Alex G.</t>
         </is>
       </c>
       <c r="I123" t="n">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>Нужны доп. фото</t>
+          <t>More photos needed</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -6768,12 +6768,12 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Борис Х.</t>
+          <t>Boris H.</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I124" t="n">
@@ -6787,7 +6787,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -6810,7 +6810,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -6820,12 +6820,12 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Тина Е.</t>
+          <t>Tina E.</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I125" t="n">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Нужны доп. фото</t>
+          <t>More photos needed</t>
         </is>
       </c>
     </row>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Юлия В.</t>
+          <t>Julia V.</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I126" t="n">
@@ -6910,7 +6910,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ольга Л.</t>
+          <t>Olga L.</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I127" t="n">
@@ -6939,7 +6939,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -6962,7 +6962,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ирина А.</t>
+          <t>Irina A.</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Алекс Г.</t>
+          <t>Alex G.</t>
         </is>
       </c>
       <c r="I128" t="n">
@@ -7010,7 +7010,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Жанна В.</t>
+          <t>Jeanne V.</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>Глеб М.</t>
+          <t>Gleb M.</t>
         </is>
       </c>
       <c r="I129" t="n">
@@ -7058,7 +7058,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Проблема</t>
+          <t>Problem</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Егор Н.</t>
+          <t>Egor N.</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="I130" t="n">
@@ -7101,7 +7101,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -7111,12 +7111,12 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Вера Ш.</t>
+          <t>Vera W.</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Алекс Г.</t>
+          <t>Alex G.</t>
         </is>
       </c>
       <c r="I131" t="n">
@@ -7130,7 +7130,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>Нужны доп. фото</t>
+          <t>More photos needed</t>
         </is>
       </c>
     </row>
@@ -7153,7 +7153,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Юлия В.</t>
+          <t>Julia V.</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I132" t="n">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -7211,12 +7211,12 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Ольга Л.</t>
+          <t>Olga L.</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I133" t="n">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -7253,7 +7253,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -7263,12 +7263,12 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Егор Н.</t>
+          <t>Egor N.</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="I134" t="n">
@@ -7301,7 +7301,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Юлия В.</t>
+          <t>Julia V.</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I135" t="n">
@@ -7349,7 +7349,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -7359,12 +7359,12 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Нина Х.</t>
+          <t>Nina H.</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Глеб М.</t>
+          <t>Gleb M.</t>
         </is>
       </c>
       <c r="I136" t="n">
@@ -7397,7 +7397,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -7407,12 +7407,12 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Глеб Г.</t>
+          <t>Gleb G.</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I137" t="n">
@@ -7426,7 +7426,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>Повторная проверка</t>
+          <t>Second review</t>
         </is>
       </c>
     </row>
@@ -7449,7 +7449,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -7459,12 +7459,12 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Кирилл П.</t>
+          <t>Kirill P.</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I138" t="n">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Ева С.</t>
+          <t>Eva S.</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="I139" t="n">
@@ -7545,7 +7545,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -7555,12 +7555,12 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Дарья М.</t>
+          <t>Daria M.</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I140" t="n">
@@ -7593,7 +7593,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -7603,12 +7603,12 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Глеб Г.</t>
+          <t>Gleb G.</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I141" t="n">
@@ -7622,7 +7622,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>Нужны доп. фото</t>
+          <t>More photos needed</t>
         </is>
       </c>
     </row>
@@ -7645,7 +7645,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -7655,12 +7655,12 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Ева С.</t>
+          <t>Eva S.</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="I142" t="n">
@@ -7674,7 +7674,7 @@
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -7697,7 +7697,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Тина Е.</t>
+          <t>Tina E.</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I143" t="n">
@@ -7745,7 +7745,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Лев П.</t>
+          <t>Leo P.</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Глеб М.</t>
+          <t>Gleb M.</t>
         </is>
       </c>
       <c r="I144" t="n">
@@ -7793,7 +7793,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Олег А.</t>
+          <t>Oleg A.</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I145" t="n">
@@ -7841,7 +7841,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -7851,12 +7851,12 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Ян Г.</t>
+          <t>Yan G.</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="I146" t="n">
@@ -7870,7 +7870,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Ирина А.</t>
+          <t>Irina A.</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Алекс Г.</t>
+          <t>Alex G.</t>
         </is>
       </c>
       <c r="I147" t="n">
@@ -7941,7 +7941,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Лиана Г.</t>
+          <t>Liana G.</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I148" t="n">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -7993,7 +7993,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -8003,12 +8003,12 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Марк О.</t>
+          <t>Mark O.</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="I149" t="n">
@@ -8041,7 +8041,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Кирилл П.</t>
+          <t>Kirill P.</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I150" t="n">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Жанна В.</t>
+          <t>Jeanne V.</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Глеб М.</t>
+          <t>Gleb M.</t>
         </is>
       </c>
       <c r="I151" t="n">
@@ -8137,7 +8137,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -8147,12 +8147,12 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Ирина А.</t>
+          <t>Irina A.</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Алекс Г.</t>
+          <t>Alex G.</t>
         </is>
       </c>
       <c r="I152" t="n">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Ольга Л.</t>
+          <t>Olga L.</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I153" t="n">
@@ -8233,7 +8233,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -8243,12 +8243,12 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Роман Ш.</t>
+          <t>Roman W.</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I154" t="n">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Ник С.</t>
+          <t>Nick S.</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I155" t="n">
@@ -8333,7 +8333,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -8343,12 +8343,12 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Борис Х.</t>
+          <t>Boris H.</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I156" t="n">
@@ -8362,7 +8362,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>Повторная проверка</t>
+          <t>Second review</t>
         </is>
       </c>
     </row>
@@ -8385,7 +8385,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -8395,12 +8395,12 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Захар Л.</t>
+          <t>Zakhar L.</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I157" t="n">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Проблема</t>
+          <t>Problem</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Борис Х.</t>
+          <t>Boris H.</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I158" t="n">
@@ -8476,7 +8476,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -8486,12 +8486,12 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Майя Д.</t>
+          <t>Maya D.</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I159" t="n">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Ник С.</t>
+          <t>Nick S.</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I160" t="n">
@@ -8553,7 +8553,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -8576,7 +8576,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -8586,12 +8586,12 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Юлия В.</t>
+          <t>Julia V.</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I161" t="n">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -8634,12 +8634,12 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Глеб Г.</t>
+          <t>Gleb G.</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I162" t="n">
@@ -8653,7 +8653,7 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -8676,7 +8676,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -8686,12 +8686,12 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Жанна В.</t>
+          <t>Jeanne V.</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Глеб М.</t>
+          <t>Gleb M.</t>
         </is>
       </c>
       <c r="I163" t="n">
@@ -8705,7 +8705,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>Нужны доп. фото</t>
+          <t>More photos needed</t>
         </is>
       </c>
     </row>
@@ -8728,7 +8728,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Проблема</t>
+          <t>Problem</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -8738,12 +8738,12 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Кирилл П.</t>
+          <t>Kirill P.</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I164" t="n">
@@ -8752,7 +8752,7 @@
       <c r="K164" s="4" t="n"/>
       <c r="L164" t="inlineStr">
         <is>
-          <t>Клиент просил ускорить</t>
+          <t>Client asked to rush</t>
         </is>
       </c>
     </row>
@@ -8775,7 +8775,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -8785,12 +8785,12 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Вера Ш.</t>
+          <t>Vera W.</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Алекс Г.</t>
+          <t>Alex G.</t>
         </is>
       </c>
       <c r="I165" t="n">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -8827,7 +8827,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -8837,12 +8837,12 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Майя Д.</t>
+          <t>Maya D.</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I166" t="n">
@@ -8875,7 +8875,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -8885,12 +8885,12 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Лев П.</t>
+          <t>Leo P.</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Глеб М.</t>
+          <t>Gleb M.</t>
         </is>
       </c>
       <c r="I167" t="n">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>Повторная проверка</t>
+          <t>Second review</t>
         </is>
       </c>
     </row>
@@ -8927,7 +8927,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Софья С.</t>
+          <t>Sofia S.</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I168" t="n">
@@ -8956,7 +8956,7 @@
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>Нужны доп. фото</t>
+          <t>More photos needed</t>
         </is>
       </c>
     </row>
@@ -8979,7 +8979,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -8989,12 +8989,12 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Юлия В.</t>
+          <t>Julia V.</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I169" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Проблема</t>
+          <t>Problem</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Вера Ш.</t>
+          <t>Vera W.</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Алекс Г.</t>
+          <t>Alex G.</t>
         </is>
       </c>
       <c r="I170" t="n">
@@ -9070,7 +9070,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -9080,12 +9080,12 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Анна П.</t>
+          <t>Anna P.</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Глеб М.</t>
+          <t>Gleb M.</t>
         </is>
       </c>
       <c r="I171" t="n">
@@ -9118,7 +9118,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Алекс Л.</t>
+          <t>Alex L.</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Алекс Г.</t>
+          <t>Alex G.</t>
         </is>
       </c>
       <c r="I172" t="n">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -9176,12 +9176,12 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Кирилл П.</t>
+          <t>Kirill P.</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I173" t="n">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -9224,12 +9224,12 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Ник С.</t>
+          <t>Nick S.</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I174" t="n">
@@ -9243,7 +9243,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>Клиент просил ускорить</t>
+          <t>Client asked to rush</t>
         </is>
       </c>
     </row>
@@ -9266,7 +9266,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Проблема</t>
+          <t>Problem</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Лиана Г.</t>
+          <t>Liana G.</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I175" t="n">
@@ -9309,7 +9309,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -9319,12 +9319,12 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Роман Ш.</t>
+          <t>Roman W.</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I176" t="n">
@@ -9338,7 +9338,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -9361,7 +9361,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -9371,12 +9371,12 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Борис Х.</t>
+          <t>Boris H.</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I177" t="n">
@@ -9409,7 +9409,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -9419,12 +9419,12 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Юлия В.</t>
+          <t>Julia V.</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I178" t="n">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>Повторная проверка</t>
+          <t>Second review</t>
         </is>
       </c>
     </row>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Марк О.</t>
+          <t>Mark O.</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="I179" t="n">
@@ -9509,7 +9509,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -9519,12 +9519,12 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Фёдор С.</t>
+          <t>Fedor S.</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I180" t="n">
@@ -9538,7 +9538,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>Повторная проверка</t>
+          <t>Second review</t>
         </is>
       </c>
     </row>
@@ -9561,7 +9561,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -9571,12 +9571,12 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Алекс Л.</t>
+          <t>Alex L.</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Алекс Г.</t>
+          <t>Alex G.</t>
         </is>
       </c>
       <c r="I181" t="n">
@@ -9590,7 +9590,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -9613,7 +9613,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>В работе</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -9623,12 +9623,12 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Олег А.</t>
+          <t>Oleg A.</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I182" t="n">
@@ -9637,7 +9637,7 @@
       <c r="K182" s="4" t="n"/>
       <c r="L182" t="inlineStr">
         <is>
-          <t>Повторная проверка</t>
+          <t>Second review</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>На проверке</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -9670,12 +9670,12 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Олег А.</t>
+          <t>Oleg A.</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I183" t="n">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>В работе</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -9713,12 +9713,12 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Ольга Л.</t>
+          <t>Olga L.</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I184" t="n">
@@ -9727,7 +9727,7 @@
       <c r="K184" s="4" t="n"/>
       <c r="L184" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9750,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -9760,12 +9760,12 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Фёдор С.</t>
+          <t>Fedor S.</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I185" t="n">
@@ -9798,7 +9798,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>В работе</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Лиана Г.</t>
+          <t>Liana G.</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I186" t="n">
@@ -9822,7 +9822,7 @@
       <c r="K186" s="4" t="n"/>
       <c r="L186" t="inlineStr">
         <is>
-          <t>Сложный план этажа</t>
+          <t>Complex floor plan</t>
         </is>
       </c>
     </row>
@@ -9845,7 +9845,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -9855,12 +9855,12 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Кирилл П.</t>
+          <t>Kirill P.</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I187" t="n">
@@ -9893,7 +9893,7 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>В работе</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Лев П.</t>
+          <t>Leo P.</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Глеб М.</t>
+          <t>Gleb M.</t>
         </is>
       </c>
       <c r="I188" t="n">
@@ -9917,7 +9917,7 @@
       <c r="K188" s="4" t="n"/>
       <c r="L188" t="inlineStr">
         <is>
-          <t>Клиент просил ускорить</t>
+          <t>Client asked to rush</t>
         </is>
       </c>
     </row>
@@ -9940,7 +9940,7 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -9950,12 +9950,12 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Ник С.</t>
+          <t>Nick S.</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I189" t="n">
@@ -9988,7 +9988,7 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>В работе</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -9998,12 +9998,12 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Глеб Г.</t>
+          <t>Gleb G.</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I190" t="n">
@@ -10012,7 +10012,7 @@
       <c r="K190" s="4" t="n"/>
       <c r="L190" t="inlineStr">
         <is>
-          <t>Нужны доп. фото</t>
+          <t>More photos needed</t>
         </is>
       </c>
     </row>
@@ -10035,7 +10035,7 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Ник С.</t>
+          <t>Nick S.</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I191" t="n">
@@ -10083,7 +10083,7 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>В работе</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Юлия В.</t>
+          <t>Julia V.</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="I192" t="n">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>На проверке</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -10136,12 +10136,12 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Глеб Г.</t>
+          <t>Gleb G.</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I193" t="n">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -10179,12 +10179,12 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Егор Н.</t>
+          <t>Egor N.</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="I194" t="n">
@@ -10217,7 +10217,7 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>В работе</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
@@ -10227,12 +10227,12 @@
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Фёдор С.</t>
+          <t>Fedor S.</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I195" t="n">
@@ -10241,7 +10241,7 @@
       <c r="K195" s="4" t="n"/>
       <c r="L195" t="inlineStr">
         <is>
-          <t>Нужны доп. фото</t>
+          <t>More photos needed</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -10274,12 +10274,12 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Глеб Г.</t>
+          <t>Gleb G.</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I196" t="n">
@@ -10312,7 +10312,7 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>На проверке</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -10322,12 +10322,12 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Роман Ш.</t>
+          <t>Roman W.</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I197" t="n">
@@ -10336,7 +10336,7 @@
       <c r="K197" s="4" t="n"/>
       <c r="L197" t="inlineStr">
         <is>
-          <t>Клиент просил ускорить</t>
+          <t>Client asked to rush</t>
         </is>
       </c>
     </row>
@@ -10359,7 +10359,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Егор Н.</t>
+          <t>Egor N.</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="I198" t="n">
@@ -10407,7 +10407,7 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -10417,12 +10417,12 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Ян Г.</t>
+          <t>Yan G.</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="I199" t="n">
@@ -10455,7 +10455,7 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>На проверке</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -10465,12 +10465,12 @@
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Ольга Л.</t>
+          <t>Olga L.</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="I200" t="n">
@@ -10498,7 +10498,7 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>В работе</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -10508,12 +10508,12 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Глеб Г.</t>
+          <t>Gleb G.</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="I201" t="n">
@@ -10554,27 +10554,27 @@
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>Имя</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Роль</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Команда</t>
+          <t>Team</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Страна</t>
+          <t>Country</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Супервайзер</t>
+          <t>Supervisor</t>
         </is>
       </c>
       <c r="G1" s="3" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="H1" s="3" t="inlineStr">
         <is>
-          <t>Дата начала</t>
+          <t>Start Date</t>
         </is>
       </c>
     </row>
@@ -10596,12 +10596,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Анна П.</t>
+          <t>Anna P.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Составитель</t>
+          <t>Drafter</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -10611,12 +10611,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Польша</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Глеб М.</t>
+          <t>Gleb M.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -10636,12 +10636,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Борис Х.</t>
+          <t>Boris H.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Составитель</t>
+          <t>Drafter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -10651,12 +10651,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Армения</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -10676,12 +10676,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Вера Ш.</t>
+          <t>Vera W.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Составитель</t>
+          <t>Drafter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -10691,12 +10691,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Грузия</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Алекс Г.</t>
+          <t>Alex G.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Глеб Г.</t>
+          <t>Gleb G.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Составитель</t>
+          <t>Drafter</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Грузия</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -10756,12 +10756,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Дарья М.</t>
+          <t>Daria M.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Составитель</t>
+          <t>Drafter</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -10771,12 +10771,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Сербия</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -10796,12 +10796,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Егор Н.</t>
+          <t>Egor N.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Составитель</t>
+          <t>Drafter</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -10811,12 +10811,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Сербия</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -10836,12 +10836,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Жанна В.</t>
+          <t>Jeanne V.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Составитель</t>
+          <t>Drafter</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -10851,12 +10851,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Грузия</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Глеб М.</t>
+          <t>Gleb M.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Захар Л.</t>
+          <t>Zakhar L.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Составитель</t>
+          <t>Drafter</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -10891,12 +10891,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Армения</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -10916,12 +10916,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Ирина А.</t>
+          <t>Irina A.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Составитель</t>
+          <t>Drafter</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Казахстан</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Алекс Г.</t>
+          <t>Alex G.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -10956,12 +10956,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Кирилл П.</t>
+          <t>Kirill P.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Составитель</t>
+          <t>Drafter</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Сербия</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -10996,12 +10996,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Лиана Г.</t>
+          <t>Liana G.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Составитель</t>
+          <t>Drafter</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -11011,12 +11011,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Польша</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -11036,12 +11036,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Марк О.</t>
+          <t>Mark O.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Составитель</t>
+          <t>Drafter</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -11051,12 +11051,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Казахстан</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -11076,12 +11076,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Нина Х.</t>
+          <t>Nina H.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Составитель</t>
+          <t>Drafter</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -11091,12 +11091,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Польша</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Глеб М.</t>
+          <t>Gleb M.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -11116,12 +11116,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Олег А.</t>
+          <t>Oleg A.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Составитель</t>
+          <t>Drafter</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -11131,12 +11131,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Армения</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -11156,12 +11156,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Полина Б.</t>
+          <t>Polina B.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Составитель</t>
+          <t>Drafter</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -11171,12 +11171,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Узбекистан</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Алекс Г.</t>
+          <t>Alex G.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -11196,12 +11196,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Роман Ш.</t>
+          <t>Roman W.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Составитель</t>
+          <t>Drafter</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -11211,12 +11211,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Сербия</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -11236,12 +11236,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Софья С.</t>
+          <t>Sofia S.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Составитель</t>
+          <t>Drafter</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -11251,12 +11251,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Грузия</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -11276,12 +11276,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Тимур С.</t>
+          <t>Timur S.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Составитель</t>
+          <t>Drafter</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -11291,12 +11291,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Казахстан</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -11316,12 +11316,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ульяна Л.</t>
+          <t>Ulyana L.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Составитель</t>
+          <t>Drafter</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -11331,12 +11331,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Узбекистан</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Глеб М.</t>
+          <t>Gleb M.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -11356,12 +11356,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Фёдор С.</t>
+          <t>Fedor S.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Составитель</t>
+          <t>Drafter</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -11371,12 +11371,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Сербия</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -11396,12 +11396,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Алекс Л.</t>
+          <t>Alex L.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Составитель</t>
+          <t>Drafter</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -11411,12 +11411,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Грузия</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Алекс Г.</t>
+          <t>Alex G.</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -11436,12 +11436,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Майя Д.</t>
+          <t>Maya D.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Составитель</t>
+          <t>Drafter</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -11451,12 +11451,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Сербия</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ник С.</t>
+          <t>Nick S.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Составитель</t>
+          <t>Drafter</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Армения</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ева С.</t>
+          <t>Eva S.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Составитель</t>
+          <t>Drafter</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Польша</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -11556,12 +11556,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Лев П.</t>
+          <t>Leo P.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Составитель</t>
+          <t>Drafter</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Узбекистан</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Глеб М.</t>
+          <t>Gleb M.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -11596,12 +11596,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Ольга Л.</t>
+          <t>Olga L.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Составитель</t>
+          <t>Drafter</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -11611,12 +11611,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Сербия</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Софья Т.</t>
+          <t>Sofia T.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11636,12 +11636,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Сергей Р.</t>
+          <t>Sergey R.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Составитель</t>
+          <t>Drafter</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -11651,12 +11651,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Казахстан</t>
+          <t>Kazakhstan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Алекс Г.</t>
+          <t>Alex G.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -11676,12 +11676,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Тина Е.</t>
+          <t>Tina E.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Составитель</t>
+          <t>Drafter</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Узбекистан</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Юлия И.</t>
+          <t>Julia I.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -11716,12 +11716,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Юлия В.</t>
+          <t>Julia V.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Составитель</t>
+          <t>Drafter</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Сербия</t>
+          <t>Serbia</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Юлия Ш.</t>
+          <t>Julia W.</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ян Г.</t>
+          <t>Yan G.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Составитель</t>
+          <t>Drafter</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -11771,12 +11771,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Узбекистан</t>
+          <t>Uzbekistan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Фёдор Ф.</t>
+          <t>Fedor F.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -11812,7 +11812,7 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Неделя с</t>
+          <t>Week Of</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
@@ -11822,17 +11822,17 @@
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Имя</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Рабочие часы</t>
+          <t>Worked Hours</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Залогированные часы</t>
+          <t>Logged Hours</t>
         </is>
       </c>
     </row>
@@ -11847,7 +11847,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Анна П.</t>
+          <t>Anna P.</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -11868,7 +11868,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Борис Х.</t>
+          <t>Boris H.</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -11889,7 +11889,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Вера Ш.</t>
+          <t>Vera W.</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -11910,7 +11910,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Глеб Г.</t>
+          <t>Gleb G.</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -11931,7 +11931,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Дарья М.</t>
+          <t>Daria M.</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -11952,7 +11952,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Егор Н.</t>
+          <t>Egor N.</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -11973,7 +11973,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Жанна В.</t>
+          <t>Jeanne V.</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -11994,7 +11994,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Захар Л.</t>
+          <t>Zakhar L.</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ирина А.</t>
+          <t>Irina A.</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Кирилл П.</t>
+          <t>Kirill P.</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -12057,7 +12057,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Лиана Г.</t>
+          <t>Liana G.</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Марк О.</t>
+          <t>Mark O.</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -12099,7 +12099,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Нина Х.</t>
+          <t>Nina H.</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Олег А.</t>
+          <t>Oleg A.</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -12141,7 +12141,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Полина Б.</t>
+          <t>Polina B.</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -12162,7 +12162,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Роман Ш.</t>
+          <t>Roman W.</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -12183,7 +12183,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Софья С.</t>
+          <t>Sofia S.</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Тимур С.</t>
+          <t>Timur S.</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -12225,7 +12225,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Ульяна Л.</t>
+          <t>Ulyana L.</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Фёдор С.</t>
+          <t>Fedor S.</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -12267,7 +12267,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Алекс Л.</t>
+          <t>Alex L.</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -12288,7 +12288,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Майя Д.</t>
+          <t>Maya D.</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -12309,7 +12309,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ник С.</t>
+          <t>Nick S.</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ева С.</t>
+          <t>Eva S.</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -12351,7 +12351,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Лев П.</t>
+          <t>Leo P.</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ольга Л.</t>
+          <t>Olga L.</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -12393,7 +12393,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Сергей Р.</t>
+          <t>Sergey R.</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Тина Е.</t>
+          <t>Tina E.</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Юлия В.</t>
+          <t>Julia V.</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -12456,7 +12456,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ян Г.</t>
+          <t>Yan G.</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -12477,7 +12477,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Анна П.</t>
+          <t>Anna P.</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -12498,7 +12498,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Борис Х.</t>
+          <t>Boris H.</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -12519,7 +12519,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Вера Ш.</t>
+          <t>Vera W.</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -12540,7 +12540,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Глеб Г.</t>
+          <t>Gleb G.</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Дарья М.</t>
+          <t>Daria M.</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -12582,7 +12582,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Егор Н.</t>
+          <t>Egor N.</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -12603,7 +12603,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Жанна В.</t>
+          <t>Jeanne V.</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -12624,7 +12624,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Захар Л.</t>
+          <t>Zakhar L.</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -12645,7 +12645,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ирина А.</t>
+          <t>Irina A.</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -12666,7 +12666,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Кирилл П.</t>
+          <t>Kirill P.</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -12687,7 +12687,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Лиана Г.</t>
+          <t>Liana G.</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Марк О.</t>
+          <t>Mark O.</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -12729,7 +12729,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Нина Х.</t>
+          <t>Nina H.</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -12750,7 +12750,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Олег А.</t>
+          <t>Oleg A.</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -12771,7 +12771,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Полина Б.</t>
+          <t>Polina B.</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -12792,7 +12792,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Роман Ш.</t>
+          <t>Roman W.</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -12813,7 +12813,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Софья С.</t>
+          <t>Sofia S.</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Тимур С.</t>
+          <t>Timur S.</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -12855,7 +12855,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ульяна Л.</t>
+          <t>Ulyana L.</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -12876,7 +12876,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Фёдор С.</t>
+          <t>Fedor S.</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -12897,7 +12897,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Алекс Л.</t>
+          <t>Alex L.</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -12918,7 +12918,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Майя Д.</t>
+          <t>Maya D.</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -12939,7 +12939,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ник С.</t>
+          <t>Nick S.</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -12960,7 +12960,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ева С.</t>
+          <t>Eva S.</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -12981,7 +12981,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Лев П.</t>
+          <t>Leo P.</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -13002,7 +13002,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ольга Л.</t>
+          <t>Olga L.</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -13023,7 +13023,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Сергей Р.</t>
+          <t>Sergey R.</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -13044,7 +13044,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Тина Е.</t>
+          <t>Tina E.</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -13065,7 +13065,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Юлия В.</t>
+          <t>Julia V.</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -13086,7 +13086,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ян Г.</t>
+          <t>Yan G.</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -13107,7 +13107,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Анна П.</t>
+          <t>Anna P.</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Борис Х.</t>
+          <t>Boris H.</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -13149,7 +13149,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Вера Ш.</t>
+          <t>Vera W.</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -13170,7 +13170,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Глеб Г.</t>
+          <t>Gleb G.</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Дарья М.</t>
+          <t>Daria M.</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -13212,7 +13212,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Егор Н.</t>
+          <t>Egor N.</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -13233,7 +13233,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Жанна В.</t>
+          <t>Jeanne V.</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -13254,7 +13254,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Захар Л.</t>
+          <t>Zakhar L.</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ирина А.</t>
+          <t>Irina A.</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Кирилл П.</t>
+          <t>Kirill P.</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -13317,7 +13317,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Лиана Г.</t>
+          <t>Liana G.</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -13338,7 +13338,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Марк О.</t>
+          <t>Mark O.</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -13359,7 +13359,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Нина Х.</t>
+          <t>Nina H.</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Олег А.</t>
+          <t>Oleg A.</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -13401,7 +13401,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Полина Б.</t>
+          <t>Polina B.</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -13422,7 +13422,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Роман Ш.</t>
+          <t>Roman W.</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -13443,7 +13443,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Софья С.</t>
+          <t>Sofia S.</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -13464,7 +13464,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Тимур С.</t>
+          <t>Timur S.</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -13485,7 +13485,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ульяна Л.</t>
+          <t>Ulyana L.</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -13506,7 +13506,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Фёдор С.</t>
+          <t>Fedor S.</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -13527,7 +13527,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Алекс Л.</t>
+          <t>Alex L.</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -13548,7 +13548,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Майя Д.</t>
+          <t>Maya D.</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -13569,7 +13569,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ник С.</t>
+          <t>Nick S.</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -13590,7 +13590,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ева С.</t>
+          <t>Eva S.</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -13611,7 +13611,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Лев П.</t>
+          <t>Leo P.</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -13632,7 +13632,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Ольга Л.</t>
+          <t>Olga L.</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -13653,7 +13653,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Сергей Р.</t>
+          <t>Sergey R.</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -13674,7 +13674,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Тина Е.</t>
+          <t>Tina E.</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -13695,7 +13695,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Юлия В.</t>
+          <t>Julia V.</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -13716,7 +13716,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ян Г.</t>
+          <t>Yan G.</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -13737,7 +13737,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Анна П.</t>
+          <t>Anna P.</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -13758,7 +13758,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Борис Х.</t>
+          <t>Boris H.</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Вера Ш.</t>
+          <t>Vera W.</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -13800,7 +13800,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Глеб Г.</t>
+          <t>Gleb G.</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -13821,7 +13821,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Дарья М.</t>
+          <t>Daria M.</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -13842,7 +13842,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Егор Н.</t>
+          <t>Egor N.</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -13863,7 +13863,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Жанна В.</t>
+          <t>Jeanne V.</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -13884,7 +13884,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Захар Л.</t>
+          <t>Zakhar L.</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ирина А.</t>
+          <t>Irina A.</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -13926,7 +13926,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Кирилл П.</t>
+          <t>Kirill P.</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -13947,7 +13947,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Лиана Г.</t>
+          <t>Liana G.</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -13968,7 +13968,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Марк О.</t>
+          <t>Mark O.</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -13989,7 +13989,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Нина Х.</t>
+          <t>Nina H.</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Олег А.</t>
+          <t>Oleg A.</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -14031,7 +14031,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Полина Б.</t>
+          <t>Polina B.</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -14052,7 +14052,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Роман Ш.</t>
+          <t>Roman W.</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -14073,7 +14073,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Софья С.</t>
+          <t>Sofia S.</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -14094,7 +14094,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Тимур С.</t>
+          <t>Timur S.</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -14115,7 +14115,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ульяна Л.</t>
+          <t>Ulyana L.</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -14136,7 +14136,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Фёдор С.</t>
+          <t>Fedor S.</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -14157,7 +14157,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Алекс Л.</t>
+          <t>Alex L.</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Майя Д.</t>
+          <t>Maya D.</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -14199,7 +14199,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Ник С.</t>
+          <t>Nick S.</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -14220,7 +14220,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ева С.</t>
+          <t>Eva S.</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -14241,7 +14241,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Лев П.</t>
+          <t>Leo P.</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Ольга Л.</t>
+          <t>Olga L.</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -14283,7 +14283,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Сергей Р.</t>
+          <t>Sergey R.</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -14304,7 +14304,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Тина Е.</t>
+          <t>Tina E.</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -14325,7 +14325,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Юлия В.</t>
+          <t>Julia V.</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ян Г.</t>
+          <t>Yan G.</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -14367,7 +14367,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Анна П.</t>
+          <t>Anna P.</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -14388,7 +14388,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Борис Х.</t>
+          <t>Boris H.</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -14409,7 +14409,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Вера Ш.</t>
+          <t>Vera W.</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Глеб Г.</t>
+          <t>Gleb G.</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -14451,7 +14451,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Дарья М.</t>
+          <t>Daria M.</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -14472,7 +14472,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Егор Н.</t>
+          <t>Egor N.</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -14493,7 +14493,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Жанна В.</t>
+          <t>Jeanne V.</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -14514,7 +14514,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Захар Л.</t>
+          <t>Zakhar L.</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -14535,7 +14535,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Ирина А.</t>
+          <t>Irina A.</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -14556,7 +14556,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Кирилл П.</t>
+          <t>Kirill P.</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -14577,7 +14577,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Лиана Г.</t>
+          <t>Liana G.</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -14598,7 +14598,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Марк О.</t>
+          <t>Mark O.</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -14619,7 +14619,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Нина Х.</t>
+          <t>Nina H.</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Олег А.</t>
+          <t>Oleg A.</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -14661,7 +14661,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Полина Б.</t>
+          <t>Polina B.</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -14682,7 +14682,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Роман Ш.</t>
+          <t>Roman W.</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -14703,7 +14703,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Софья С.</t>
+          <t>Sofia S.</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -14724,7 +14724,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Тимур С.</t>
+          <t>Timur S.</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -14745,7 +14745,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Ульяна Л.</t>
+          <t>Ulyana L.</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Фёдор С.</t>
+          <t>Fedor S.</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -14787,7 +14787,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Алекс Л.</t>
+          <t>Alex L.</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -14808,7 +14808,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Майя Д.</t>
+          <t>Maya D.</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -14829,7 +14829,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Ник С.</t>
+          <t>Nick S.</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Ева С.</t>
+          <t>Eva S.</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -14871,7 +14871,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Лев П.</t>
+          <t>Leo P.</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -14892,7 +14892,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Ольга Л.</t>
+          <t>Olga L.</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -14913,7 +14913,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Сергей Р.</t>
+          <t>Sergey R.</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -14934,7 +14934,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Тина Е.</t>
+          <t>Tina E.</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -14955,7 +14955,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Юлия В.</t>
+          <t>Julia V.</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -14976,7 +14976,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Ян Г.</t>
+          <t>Yan G.</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -14997,7 +14997,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Анна П.</t>
+          <t>Anna P.</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -15018,7 +15018,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Борис Х.</t>
+          <t>Boris H.</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -15039,7 +15039,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Вера Ш.</t>
+          <t>Vera W.</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -15060,7 +15060,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Глеб Г.</t>
+          <t>Gleb G.</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Дарья М.</t>
+          <t>Daria M.</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -15102,7 +15102,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Егор Н.</t>
+          <t>Egor N.</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Жанна В.</t>
+          <t>Jeanne V.</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -15144,7 +15144,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Захар Л.</t>
+          <t>Zakhar L.</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -15165,7 +15165,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Ирина А.</t>
+          <t>Irina A.</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -15186,7 +15186,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Кирилл П.</t>
+          <t>Kirill P.</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -15207,7 +15207,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Лиана Г.</t>
+          <t>Liana G.</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Марк О.</t>
+          <t>Mark O.</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -15249,7 +15249,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Нина Х.</t>
+          <t>Nina H.</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -15270,7 +15270,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Олег А.</t>
+          <t>Oleg A.</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -15291,7 +15291,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Полина Б.</t>
+          <t>Polina B.</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -15312,7 +15312,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Роман Ш.</t>
+          <t>Roman W.</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -15333,7 +15333,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Софья С.</t>
+          <t>Sofia S.</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -15354,7 +15354,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Тимур С.</t>
+          <t>Timur S.</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Ульяна Л.</t>
+          <t>Ulyana L.</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -15396,7 +15396,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Фёдор С.</t>
+          <t>Fedor S.</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -15417,7 +15417,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Алекс Л.</t>
+          <t>Alex L.</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -15438,7 +15438,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Майя Д.</t>
+          <t>Maya D.</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -15459,7 +15459,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Ник С.</t>
+          <t>Nick S.</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -15480,7 +15480,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Ева С.</t>
+          <t>Eva S.</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -15501,7 +15501,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Лев П.</t>
+          <t>Leo P.</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -15522,7 +15522,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Ольга Л.</t>
+          <t>Olga L.</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -15543,7 +15543,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Сергей Р.</t>
+          <t>Sergey R.</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -15564,7 +15564,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Тина Е.</t>
+          <t>Tina E.</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Юлия В.</t>
+          <t>Julia V.</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -15606,7 +15606,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Ян Г.</t>
+          <t>Yan G.</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -15627,7 +15627,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Анна П.</t>
+          <t>Anna P.</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -15648,7 +15648,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Борис Х.</t>
+          <t>Boris H.</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -15669,7 +15669,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Вера Ш.</t>
+          <t>Vera W.</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -15690,7 +15690,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Глеб Г.</t>
+          <t>Gleb G.</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -15711,7 +15711,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Дарья М.</t>
+          <t>Daria M.</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -15732,7 +15732,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Егор Н.</t>
+          <t>Egor N.</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -15753,7 +15753,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Жанна В.</t>
+          <t>Jeanne V.</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -15774,7 +15774,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Захар Л.</t>
+          <t>Zakhar L.</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -15795,7 +15795,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Ирина А.</t>
+          <t>Irina A.</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -15816,7 +15816,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Кирилл П.</t>
+          <t>Kirill P.</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -15837,7 +15837,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Лиана Г.</t>
+          <t>Liana G.</t>
         </is>
       </c>
       <c r="D192" t="n">
@@ -15858,7 +15858,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Марк О.</t>
+          <t>Mark O.</t>
         </is>
       </c>
       <c r="D193" t="n">
@@ -15879,7 +15879,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Нина Х.</t>
+          <t>Nina H.</t>
         </is>
       </c>
       <c r="D194" t="n">
@@ -15900,7 +15900,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Олег А.</t>
+          <t>Oleg A.</t>
         </is>
       </c>
       <c r="D195" t="n">
@@ -15921,7 +15921,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Полина Б.</t>
+          <t>Polina B.</t>
         </is>
       </c>
       <c r="D196" t="n">
@@ -15942,7 +15942,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Роман Ш.</t>
+          <t>Roman W.</t>
         </is>
       </c>
       <c r="D197" t="n">
@@ -15963,7 +15963,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Софья С.</t>
+          <t>Sofia S.</t>
         </is>
       </c>
       <c r="D198" t="n">
@@ -15984,7 +15984,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Тимур С.</t>
+          <t>Timur S.</t>
         </is>
       </c>
       <c r="D199" t="n">
@@ -16005,7 +16005,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Ульяна Л.</t>
+          <t>Ulyana L.</t>
         </is>
       </c>
       <c r="D200" t="n">
@@ -16026,7 +16026,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Фёдор С.</t>
+          <t>Fedor S.</t>
         </is>
       </c>
       <c r="D201" t="n">
@@ -16047,7 +16047,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Алекс Л.</t>
+          <t>Alex L.</t>
         </is>
       </c>
       <c r="D202" t="n">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Майя Д.</t>
+          <t>Maya D.</t>
         </is>
       </c>
       <c r="D203" t="n">
@@ -16089,7 +16089,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Ник С.</t>
+          <t>Nick S.</t>
         </is>
       </c>
       <c r="D204" t="n">
@@ -16110,7 +16110,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Ева С.</t>
+          <t>Eva S.</t>
         </is>
       </c>
       <c r="D205" t="n">
@@ -16131,7 +16131,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Лев П.</t>
+          <t>Leo P.</t>
         </is>
       </c>
       <c r="D206" t="n">
@@ -16152,7 +16152,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Ольга Л.</t>
+          <t>Olga L.</t>
         </is>
       </c>
       <c r="D207" t="n">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Сергей Р.</t>
+          <t>Sergey R.</t>
         </is>
       </c>
       <c r="D208" t="n">
@@ -16194,7 +16194,7 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Тина Е.</t>
+          <t>Tina E.</t>
         </is>
       </c>
       <c r="D209" t="n">
@@ -16215,7 +16215,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Юлия В.</t>
+          <t>Julia V.</t>
         </is>
       </c>
       <c r="D210" t="n">
@@ -16236,7 +16236,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Ян Г.</t>
+          <t>Yan G.</t>
         </is>
       </c>
       <c r="D211" t="n">
@@ -16257,7 +16257,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Анна П.</t>
+          <t>Anna P.</t>
         </is>
       </c>
       <c r="D212" t="n">
@@ -16278,7 +16278,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Борис Х.</t>
+          <t>Boris H.</t>
         </is>
       </c>
       <c r="D213" t="n">
@@ -16299,7 +16299,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Вера Ш.</t>
+          <t>Vera W.</t>
         </is>
       </c>
       <c r="D214" t="n">
@@ -16320,7 +16320,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Глеб Г.</t>
+          <t>Gleb G.</t>
         </is>
       </c>
       <c r="D215" t="n">
@@ -16341,7 +16341,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Дарья М.</t>
+          <t>Daria M.</t>
         </is>
       </c>
       <c r="D216" t="n">
@@ -16362,7 +16362,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Егор Н.</t>
+          <t>Egor N.</t>
         </is>
       </c>
       <c r="D217" t="n">
@@ -16383,7 +16383,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Жанна В.</t>
+          <t>Jeanne V.</t>
         </is>
       </c>
       <c r="D218" t="n">
@@ -16404,7 +16404,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Захар Л.</t>
+          <t>Zakhar L.</t>
         </is>
       </c>
       <c r="D219" t="n">
@@ -16425,7 +16425,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Ирина А.</t>
+          <t>Irina A.</t>
         </is>
       </c>
       <c r="D220" t="n">
@@ -16446,7 +16446,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Кирилл П.</t>
+          <t>Kirill P.</t>
         </is>
       </c>
       <c r="D221" t="n">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Лиана Г.</t>
+          <t>Liana G.</t>
         </is>
       </c>
       <c r="D222" t="n">
@@ -16488,7 +16488,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Марк О.</t>
+          <t>Mark O.</t>
         </is>
       </c>
       <c r="D223" t="n">
@@ -16509,7 +16509,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Нина Х.</t>
+          <t>Nina H.</t>
         </is>
       </c>
       <c r="D224" t="n">
@@ -16530,7 +16530,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Олег А.</t>
+          <t>Oleg A.</t>
         </is>
       </c>
       <c r="D225" t="n">
@@ -16551,7 +16551,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Полина Б.</t>
+          <t>Polina B.</t>
         </is>
       </c>
       <c r="D226" t="n">
@@ -16572,7 +16572,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Роман Ш.</t>
+          <t>Roman W.</t>
         </is>
       </c>
       <c r="D227" t="n">
@@ -16593,7 +16593,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Софья С.</t>
+          <t>Sofia S.</t>
         </is>
       </c>
       <c r="D228" t="n">
@@ -16614,7 +16614,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Тимур С.</t>
+          <t>Timur S.</t>
         </is>
       </c>
       <c r="D229" t="n">
@@ -16635,7 +16635,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Ульяна Л.</t>
+          <t>Ulyana L.</t>
         </is>
       </c>
       <c r="D230" t="n">
@@ -16656,7 +16656,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Фёдор С.</t>
+          <t>Fedor S.</t>
         </is>
       </c>
       <c r="D231" t="n">
@@ -16677,7 +16677,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Алекс Л.</t>
+          <t>Alex L.</t>
         </is>
       </c>
       <c r="D232" t="n">
@@ -16698,7 +16698,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Майя Д.</t>
+          <t>Maya D.</t>
         </is>
       </c>
       <c r="D233" t="n">
@@ -16719,7 +16719,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Ник С.</t>
+          <t>Nick S.</t>
         </is>
       </c>
       <c r="D234" t="n">
@@ -16740,7 +16740,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Ева С.</t>
+          <t>Eva S.</t>
         </is>
       </c>
       <c r="D235" t="n">
@@ -16761,7 +16761,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Лев П.</t>
+          <t>Leo P.</t>
         </is>
       </c>
       <c r="D236" t="n">
@@ -16782,7 +16782,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Ольга Л.</t>
+          <t>Olga L.</t>
         </is>
       </c>
       <c r="D237" t="n">
@@ -16803,7 +16803,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Сергей Р.</t>
+          <t>Sergey R.</t>
         </is>
       </c>
       <c r="D238" t="n">
@@ -16824,7 +16824,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Тина Е.</t>
+          <t>Tina E.</t>
         </is>
       </c>
       <c r="D239" t="n">
@@ -16845,7 +16845,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Юлия В.</t>
+          <t>Julia V.</t>
         </is>
       </c>
       <c r="D240" t="n">
@@ -16866,7 +16866,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Ян Г.</t>
+          <t>Yan G.</t>
         </is>
       </c>
       <c r="D241" t="n">
@@ -16905,22 +16905,22 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>исполнитель</t>
+          <t>assignee</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>статус</t>
+          <t>status</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>дата</t>
+          <t>date</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>часы</t>
+          <t>hours</t>
         </is>
       </c>
     </row>
@@ -16932,12 +16932,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Юлия В.</t>
+          <t>Julia V.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>готов</t>
+          <t>done</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -16959,12 +16959,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Тина Е.</t>
+          <t>Tina E.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -16986,12 +16986,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Софья С.</t>
+          <t>Sofia S.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>готов</t>
+          <t>done</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -17013,12 +17013,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Вера Ш.</t>
+          <t>Vera W.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -17040,12 +17040,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Юлия В.</t>
+          <t>Julia V.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ГОТОВ</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -17067,12 +17067,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Лиана Г. </t>
+          <t xml:space="preserve">  Liana G. </t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -17094,12 +17094,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Софья С.</t>
+          <t>Sofia S.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -17121,12 +17121,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Роман Ш.</t>
+          <t>Roman W.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -17149,12 +17149,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>НИК С.</t>
+          <t>NICK S.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>готов</t>
+          <t>done</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -17176,12 +17176,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Тина Е.</t>
+          <t>Tina E.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -17203,12 +17203,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Юлия В. </t>
+          <t xml:space="preserve">  Julia V. </t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -17230,12 +17230,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ник С.</t>
+          <t>Nick S.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -17257,12 +17257,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Софья С.</t>
+          <t>Sofia S.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>СЕРГЕЙ Р.</t>
+          <t>SERGEY R.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Борис Х. </t>
+          <t xml:space="preserve">  Boris H. </t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -17338,12 +17338,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Майя Д. </t>
+          <t xml:space="preserve">  Maya D. </t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -17365,12 +17365,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ник С.</t>
+          <t>Nick S.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -17392,12 +17392,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ник С.</t>
+          <t>Nick S.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -17419,12 +17419,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Вера Ш.</t>
+          <t>Vera W.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ПРОБЛЕМА</t>
+          <t>PROBLEM</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -17446,12 +17446,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Юлия В. </t>
+          <t xml:space="preserve">  Julia V. </t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -17473,12 +17473,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Дарья М. </t>
+          <t xml:space="preserve">  Daria M. </t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -17501,12 +17501,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Алекс Л.</t>
+          <t>Alex L.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -17528,12 +17528,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Жанна В. </t>
+          <t xml:space="preserve">  Jeanne V. </t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -17555,12 +17555,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Алекс Л. </t>
+          <t xml:space="preserve">  Alex L. </t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -17582,12 +17582,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Жанна В.</t>
+          <t>Jeanne V.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -17609,12 +17609,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Дарья М. </t>
+          <t xml:space="preserve">  Daria M. </t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ГОТОВ</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -17636,12 +17636,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ФЁДОР С.</t>
+          <t>FEDOR S.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>В работе</t>
+          <t>In Progress</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -17663,12 +17663,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ЮЛИЯ В.</t>
+          <t>JULIA V.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -17690,12 +17690,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Анна П.</t>
+          <t>Anna P.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -17717,12 +17717,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Роман Ш.</t>
+          <t>Roman W.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -17744,12 +17744,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Вера Ш. </t>
+          <t xml:space="preserve">  Vera W. </t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>готов</t>
+          <t>done</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -17771,12 +17771,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Глеб Г.</t>
+          <t>Gleb G.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>На проверке</t>
+          <t>In Review</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -17798,12 +17798,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Юлия В.</t>
+          <t>Julia V.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -17825,12 +17825,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Вера Ш.</t>
+          <t>Vera W.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>ГОТОВ</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -17853,12 +17853,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ФЁДОР С.</t>
+          <t>FEDOR S.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -17880,12 +17880,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Жанна В. </t>
+          <t xml:space="preserve">  Jeanne V. </t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -17907,12 +17907,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Лиана Г. </t>
+          <t xml:space="preserve">  Liana G. </t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -17934,12 +17934,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Кирилл П. </t>
+          <t xml:space="preserve">  Kirill P. </t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>готов</t>
+          <t>done</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -17961,12 +17961,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Алекс Л.</t>
+          <t>Alex L.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Готов</t>
+          <t xml:space="preserve"> Done</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -17988,12 +17988,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Ирина А. </t>
+          <t xml:space="preserve">  Irina A. </t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -18015,12 +18015,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Анна П.</t>
+          <t>Anna P.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -18042,12 +18042,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Юлия В.</t>
+          <t>Julia V.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Готов</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -18069,12 +18069,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>КИРИЛЛ П.</t>
+          <t>KIRILL P.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>готов</t>
+          <t>done</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -18096,12 +18096,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Глеб Г. </t>
+          <t xml:space="preserve">  Gleb G. </t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>готов</t>
+          <t>done</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -18123,12 +18123,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Нина Х.</t>
+          <t>Nina H.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ГОТОВ</t>
+          <t>DONE</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -18174,67 +18174,67 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>ID заказа</t>
+          <t>Order ID</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>Создан</t>
+          <t>Created</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Дедлайн</t>
+          <t>Deadline</t>
         </is>
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Тип</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Статус</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>ID исполнителя</t>
+          <t>Assignee ID</t>
         </is>
       </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Исполнитель</t>
+          <t>Assignee</t>
         </is>
       </c>
       <c r="H1" s="3" t="inlineStr">
         <is>
-          <t>Супервайзер</t>
+          <t>Supervisor</t>
         </is>
       </c>
       <c r="I1" s="3" t="inlineStr">
         <is>
-          <t>Часы</t>
+          <t>Hours</t>
         </is>
       </c>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Оценка QC</t>
+          <t>QC Score</t>
         </is>
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
-          <t>Сдан</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="L1" s="3" t="inlineStr">
         <is>
-          <t>Комментарий</t>
+          <t>Comment</t>
         </is>
       </c>
       <c r="M1" s="3" t="inlineStr">
         <is>
-          <t>Дата архивации</t>
+          <t>Archived At</t>
         </is>
       </c>
     </row>
@@ -18255,7 +18255,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Сюда скрипты модуля 8 выводят метрики и графики</t>
+          <t>Module 8 scripts write metrics and charts here</t>
         </is>
       </c>
     </row>
@@ -18281,58 +18281,58 @@
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Параметр</t>
+          <t>Parameter</t>
         </is>
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>Значение</t>
+          <t>Value</t>
         </is>
       </c>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Описание</t>
+          <t>Description</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ЛИСТ_ЗАКАЗОВ</t>
+          <t>ORDERS_SHEET</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Заказы</t>
+          <t>Orders</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Откуда скрипты берут заказы</t>
+          <t>Sheet the scripts read orders from</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ЛИСТ_АРХИВА</t>
+          <t>ARCHIVE_SHEET</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Архив</t>
+          <t>Archive</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Куда переносятся закрытые заказы</t>
+          <t>Sheet closed orders are moved to</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ПОРОГ_ПРОСРОЧКИ_Ч</t>
+          <t>HOT_HOURS</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -18340,20 +18340,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>За сколько часов до дедлайна заказ считается «горящим»</t>
+          <t>Hours before the deadline when an order counts as urgent</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>EMAIL_УВЕДОМЛЕНИЙ</t>
+          <t>NOTIFY_EMAIL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ваш email для уведомлений (модуль 5)</t>
+          <t>Your email for notifications (module 5)</t>
         </is>
       </c>
     </row>
@@ -18366,14 +18366,14 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Адрес входящего webhook Slack (модуль 5, по желанию)</t>
+          <t>Leave empty: the webhook URL lives in script properties (module 5)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ЧАСОВОЙ_ПОЯС</t>
+          <t>TIME_ZONE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -18383,7 +18383,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Часовой пояс для дат в отчётах</t>
+          <t>Time zone for dates in reports</t>
         </is>
       </c>
     </row>
